--- a/MissionReports/SOMEC_Mission_QAQC_Index_20260324.xlsx
+++ b/MissionReports/SOMEC_Mission_QAQC_Index_20260324.xlsx
@@ -9,6 +9,1016 @@
     <sheet name="Index" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="335">
+  <si>
+    <t xml:space="preserve">mission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_transects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_observations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dt_mission_start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dt_mission_end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">report_path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVI090806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2009-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2009-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/AVI090806.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOR140228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-02-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-03-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/GOR140228.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUD091025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2009-10-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2009-11-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/HUD091025.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUD101107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010-11-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010-11-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/HUD101107.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUD111102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011-11-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011-11-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/HUD111102.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUD121030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-10-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-11-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/HUD121030.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUD121106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-11-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/HUD121106.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUD131029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-10-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-11-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/HUD131029.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISL130421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-04-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-04-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/ISL130421.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLB090423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2009-04-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2009-05-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/MLB090423.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAR110727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/PAR110727.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAR111214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011-12-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011-12-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/PAR111214.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAR120312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-03-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-03-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/PAR120312.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAR120321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-03-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-03-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/PAR120321.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAR130430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-04-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-05-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/PAR130430.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PER130717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/PER130717.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL100603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL100603.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL110817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011-08-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL110817.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COR191022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-10-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-11-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/COR191022.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL190526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL190526.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL190906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL190906.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL120802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL120802.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL120905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-09-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-09-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL120905.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL120919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-09-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-09-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL120919.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL130602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-06-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL130602.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL130804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL130804.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL130904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-09-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL130904.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUD140601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/HUD140601.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUD141029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-10-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-11-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/HUD141029.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL140905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-09-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-09-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL140905.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THA140807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-08-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/THA140807.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUD151019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-10-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-11-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/HUD151019.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL150802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL150802.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL150531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-06-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL150531.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL150904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-09-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL150904.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COR160601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/COR160601.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL160902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-09-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL160902.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL160802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL160802.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUD161016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-10-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-11-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/HUD161016.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EAR170302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-03-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-03-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/EAR170302.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL170529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL170529.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COR171108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-11-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-11-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/COR171108.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL170803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-08-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-09-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL170803.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUD061028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2006-10-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2006-11-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/HUD061028.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLB070421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-04-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-05-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/MLB070421.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DES070625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-06-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/DES070625.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUD081026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008-10-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008-11-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/HUD081026.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIM070610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/SIM070610.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL070613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-06-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL070613.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAC070708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/VAC070708.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRA070709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-07-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TRA070709.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR070717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/CAR070717.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRO070718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/PRO070718.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR070722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/CAR070722.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAM070729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-07-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/CAM070729.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOR070731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/NOR070731.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOR070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-08-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/NOR070801.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAC070812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/VAC070812.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRA070813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2007-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TRA070813.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL080615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL080615.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL080828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008-08-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL080828.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL090606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2009-06-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2009-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL090606.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL090909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2009-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2009-09-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL090909.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COR180604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-06-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/COR180604.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUD181014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-10-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-10-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/HUD181014.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL180907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-09-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-09-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL180907.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL180803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-08-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL180803.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRA201204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TRA201204.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUD201019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-10-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-10-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/HUD201019.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRA200729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-10-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TRA200729.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEL220608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/TEL220608.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COR230608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/COR230608.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COR230617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-06-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/COR230617.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSM230816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-09-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/MSM230816.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COR231017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-10-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-11-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/COR231017.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COR241016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/COR241016.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIE240921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/MIE240921.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COR240607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/COR240607.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOR240802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/NOR240802.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAC070711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/VAC070711.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR240906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/CAR240906.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR250531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/CAR250531.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEL250719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/BEL250719.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMU250628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/AMU250628.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANN251013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u:/SOMEC/BaseDeDonnees/GestionDeDonnees/SOMEC_Editeur/MissionReports/ANN251013.xlsx</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -334,7 +1344,1728 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C2" t="n">
+        <v>349</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="n">
+        <v>134</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2793</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="n">
+        <v>205</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3698</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="n">
+        <v>131</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2108</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="n">
+        <v>177</v>
+      </c>
+      <c r="C7" t="n">
+        <v>971</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="n">
+        <v>21</v>
+      </c>
+      <c r="C8" t="n">
+        <v>158</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="n">
+        <v>255</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5715</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="n">
+        <v>102</v>
+      </c>
+      <c r="C10" t="n">
+        <v>846</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="n">
+        <v>266</v>
+      </c>
+      <c r="C11" t="n">
+        <v>657</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="n">
+        <v>95</v>
+      </c>
+      <c r="C12" t="n">
+        <v>889</v>
+      </c>
+      <c r="D12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="n">
+        <v>115</v>
+      </c>
+      <c r="C13" t="n">
+        <v>299</v>
+      </c>
+      <c r="D13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="n">
+        <v>492</v>
+      </c>
+      <c r="C14" t="n">
+        <v>306</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="n">
+        <v>207</v>
+      </c>
+      <c r="C15" t="n">
+        <v>267</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" t="n">
+        <v>82</v>
+      </c>
+      <c r="C16" t="n">
+        <v>698</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" t="n">
+        <v>431</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5852</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" t="n">
+        <v>156</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5663</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3044</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" t="n">
+        <v>147</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5058</v>
+      </c>
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" t="n">
+        <v>207</v>
+      </c>
+      <c r="C21" t="n">
+        <v>6329</v>
+      </c>
+      <c r="D21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" t="n">
+        <v>321</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4449</v>
+      </c>
+      <c r="D22" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" t="n">
+        <v>915</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1392</v>
+      </c>
+      <c r="D23" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" t="n">
+        <v>127</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2264</v>
+      </c>
+      <c r="D24" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" t="s">
+        <v>95</v>
+      </c>
+      <c r="F24" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" t="n">
+        <v>210</v>
+      </c>
+      <c r="C25" t="n">
+        <v>673</v>
+      </c>
+      <c r="D25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" t="s">
+        <v>99</v>
+      </c>
+      <c r="F25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>101</v>
+      </c>
+      <c r="B26" t="n">
+        <v>325</v>
+      </c>
+      <c r="C26" t="n">
+        <v>8511</v>
+      </c>
+      <c r="D26" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26" t="s">
+        <v>103</v>
+      </c>
+      <c r="F26" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" t="n">
+        <v>833</v>
+      </c>
+      <c r="C27" t="n">
+        <v>7476</v>
+      </c>
+      <c r="D27" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" t="n">
+        <v>347</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5671</v>
+      </c>
+      <c r="D28" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28" t="s">
+        <v>111</v>
+      </c>
+      <c r="F28" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" t="n">
+        <v>139</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3661</v>
+      </c>
+      <c r="D29" t="s">
+        <v>114</v>
+      </c>
+      <c r="E29" t="s">
+        <v>115</v>
+      </c>
+      <c r="F29" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" t="n">
+        <v>24</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1436</v>
+      </c>
+      <c r="D30" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F30" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" t="n">
+        <v>260</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2098</v>
+      </c>
+      <c r="D31" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" t="n">
+        <v>118</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2328</v>
+      </c>
+      <c r="D32" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" t="n">
+        <v>203</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2156</v>
+      </c>
+      <c r="D33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F33" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>133</v>
+      </c>
+      <c r="B34" t="n">
+        <v>473</v>
+      </c>
+      <c r="C34" t="n">
+        <v>7156</v>
+      </c>
+      <c r="D34" t="s">
+        <v>134</v>
+      </c>
+      <c r="E34" t="s">
+        <v>135</v>
+      </c>
+      <c r="F34" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>137</v>
+      </c>
+      <c r="B35" t="n">
+        <v>379</v>
+      </c>
+      <c r="C35" t="n">
+        <v>6432</v>
+      </c>
+      <c r="D35" t="s">
+        <v>138</v>
+      </c>
+      <c r="E35" t="s">
+        <v>139</v>
+      </c>
+      <c r="F35" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>141</v>
+      </c>
+      <c r="B36" t="n">
+        <v>311</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4368</v>
+      </c>
+      <c r="D36" t="s">
+        <v>142</v>
+      </c>
+      <c r="E36" t="s">
+        <v>143</v>
+      </c>
+      <c r="F36" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>145</v>
+      </c>
+      <c r="B37" t="n">
+        <v>479</v>
+      </c>
+      <c r="C37" t="n">
+        <v>7587</v>
+      </c>
+      <c r="D37" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" t="s">
+        <v>147</v>
+      </c>
+      <c r="F37" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>149</v>
+      </c>
+      <c r="B38" t="n">
+        <v>418</v>
+      </c>
+      <c r="C38" t="n">
+        <v>8092</v>
+      </c>
+      <c r="D38" t="s">
+        <v>150</v>
+      </c>
+      <c r="E38" t="s">
+        <v>151</v>
+      </c>
+      <c r="F38" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>153</v>
+      </c>
+      <c r="B39" t="n">
+        <v>517</v>
+      </c>
+      <c r="C39" t="n">
+        <v>7409</v>
+      </c>
+      <c r="D39" t="s">
+        <v>154</v>
+      </c>
+      <c r="E39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F39" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>157</v>
+      </c>
+      <c r="B40" t="n">
+        <v>370</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4984</v>
+      </c>
+      <c r="D40" t="s">
+        <v>158</v>
+      </c>
+      <c r="E40" t="s">
+        <v>159</v>
+      </c>
+      <c r="F40" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>161</v>
+      </c>
+      <c r="B41" t="n">
+        <v>130</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2292</v>
+      </c>
+      <c r="D41" t="s">
+        <v>162</v>
+      </c>
+      <c r="E41" t="s">
+        <v>163</v>
+      </c>
+      <c r="F41" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>165</v>
+      </c>
+      <c r="B42" t="n">
+        <v>497</v>
+      </c>
+      <c r="C42" t="n">
+        <v>10137</v>
+      </c>
+      <c r="D42" t="s">
+        <v>166</v>
+      </c>
+      <c r="E42" t="s">
+        <v>167</v>
+      </c>
+      <c r="F42" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>169</v>
+      </c>
+      <c r="B43" t="n">
+        <v>69</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2203</v>
+      </c>
+      <c r="D43" t="s">
+        <v>170</v>
+      </c>
+      <c r="E43" t="s">
+        <v>171</v>
+      </c>
+      <c r="F43" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>173</v>
+      </c>
+      <c r="B44" t="n">
+        <v>446</v>
+      </c>
+      <c r="C44" t="n">
+        <v>8555</v>
+      </c>
+      <c r="D44" t="s">
+        <v>174</v>
+      </c>
+      <c r="E44" t="s">
+        <v>175</v>
+      </c>
+      <c r="F44" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>177</v>
+      </c>
+      <c r="B45" t="n">
+        <v>115</v>
+      </c>
+      <c r="C45" t="n">
+        <v>370</v>
+      </c>
+      <c r="D45" t="s">
+        <v>178</v>
+      </c>
+      <c r="E45" t="s">
+        <v>179</v>
+      </c>
+      <c r="F45" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>181</v>
+      </c>
+      <c r="B46" t="n">
+        <v>68</v>
+      </c>
+      <c r="C46" t="n">
+        <v>600</v>
+      </c>
+      <c r="D46" t="s">
+        <v>182</v>
+      </c>
+      <c r="E46" t="s">
+        <v>183</v>
+      </c>
+      <c r="F46" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>185</v>
+      </c>
+      <c r="B47" t="n">
+        <v>36</v>
+      </c>
+      <c r="C47" t="n">
+        <v>388</v>
+      </c>
+      <c r="D47" t="s">
+        <v>186</v>
+      </c>
+      <c r="E47" t="s">
+        <v>187</v>
+      </c>
+      <c r="F47" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>189</v>
+      </c>
+      <c r="B48" t="n">
+        <v>164</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2686</v>
+      </c>
+      <c r="D48" t="s">
+        <v>190</v>
+      </c>
+      <c r="E48" t="s">
+        <v>191</v>
+      </c>
+      <c r="F48" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>193</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="n">
+        <v>12</v>
+      </c>
+      <c r="D49" t="s">
+        <v>194</v>
+      </c>
+      <c r="E49" t="s">
+        <v>194</v>
+      </c>
+      <c r="F49" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>196</v>
+      </c>
+      <c r="B50" t="n">
+        <v>239</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1585</v>
+      </c>
+      <c r="D50" t="s">
+        <v>197</v>
+      </c>
+      <c r="E50" t="s">
+        <v>198</v>
+      </c>
+      <c r="F50" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>200</v>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="n">
+        <v>184</v>
+      </c>
+      <c r="D51" t="s">
+        <v>201</v>
+      </c>
+      <c r="E51" t="s">
+        <v>201</v>
+      </c>
+      <c r="F51" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>203</v>
+      </c>
+      <c r="B52" t="n">
+        <v>8</v>
+      </c>
+      <c r="C52" t="n">
+        <v>258</v>
+      </c>
+      <c r="D52" t="s">
+        <v>204</v>
+      </c>
+      <c r="E52" t="s">
+        <v>205</v>
+      </c>
+      <c r="F52" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>207</v>
+      </c>
+      <c r="B53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" t="n">
+        <v>39</v>
+      </c>
+      <c r="D53" t="s">
+        <v>208</v>
+      </c>
+      <c r="E53" t="s">
+        <v>208</v>
+      </c>
+      <c r="F53" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>210</v>
+      </c>
+      <c r="B54" t="n">
+        <v>69</v>
+      </c>
+      <c r="C54" t="n">
+        <v>255</v>
+      </c>
+      <c r="D54" t="s">
+        <v>211</v>
+      </c>
+      <c r="E54" t="s">
+        <v>212</v>
+      </c>
+      <c r="F54" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="s">
+        <v>215</v>
+      </c>
+      <c r="E55" t="s">
+        <v>215</v>
+      </c>
+      <c r="F55" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>217</v>
+      </c>
+      <c r="B56" t="n">
+        <v>20</v>
+      </c>
+      <c r="C56" t="n">
+        <v>213</v>
+      </c>
+      <c r="D56" t="s">
+        <v>218</v>
+      </c>
+      <c r="E56" t="s">
+        <v>219</v>
+      </c>
+      <c r="F56" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>221</v>
+      </c>
+      <c r="B57" t="n">
+        <v>11</v>
+      </c>
+      <c r="C57" t="n">
+        <v>112</v>
+      </c>
+      <c r="D57" t="s">
+        <v>222</v>
+      </c>
+      <c r="E57" t="s">
+        <v>222</v>
+      </c>
+      <c r="F57" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>224</v>
+      </c>
+      <c r="B58" t="n">
+        <v>13</v>
+      </c>
+      <c r="C58" t="n">
+        <v>303</v>
+      </c>
+      <c r="D58" t="s">
+        <v>225</v>
+      </c>
+      <c r="E58" t="s">
+        <v>225</v>
+      </c>
+      <c r="F58" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>227</v>
+      </c>
+      <c r="B59" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" t="n">
+        <v>49</v>
+      </c>
+      <c r="D59" t="s">
+        <v>228</v>
+      </c>
+      <c r="E59" t="s">
+        <v>228</v>
+      </c>
+      <c r="F59" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>230</v>
+      </c>
+      <c r="B60" t="n">
+        <v>72</v>
+      </c>
+      <c r="C60" t="n">
+        <v>548</v>
+      </c>
+      <c r="D60" t="s">
+        <v>231</v>
+      </c>
+      <c r="E60" t="s">
+        <v>232</v>
+      </c>
+      <c r="F60" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>234</v>
+      </c>
+      <c r="B61" t="n">
+        <v>236</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1215</v>
+      </c>
+      <c r="D61" t="s">
+        <v>235</v>
+      </c>
+      <c r="E61" t="s">
+        <v>236</v>
+      </c>
+      <c r="F61" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>238</v>
+      </c>
+      <c r="B62" t="n">
+        <v>237</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1326</v>
+      </c>
+      <c r="D62" t="s">
+        <v>239</v>
+      </c>
+      <c r="E62" t="s">
+        <v>240</v>
+      </c>
+      <c r="F62" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>242</v>
+      </c>
+      <c r="B63" t="n">
+        <v>177</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1897</v>
+      </c>
+      <c r="D63" t="s">
+        <v>243</v>
+      </c>
+      <c r="E63" t="s">
+        <v>244</v>
+      </c>
+      <c r="F63" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>246</v>
+      </c>
+      <c r="B64" t="n">
+        <v>164</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1025</v>
+      </c>
+      <c r="D64" t="s">
+        <v>247</v>
+      </c>
+      <c r="E64" t="s">
+        <v>248</v>
+      </c>
+      <c r="F64" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>250</v>
+      </c>
+      <c r="B65" t="n">
+        <v>297</v>
+      </c>
+      <c r="C65" t="n">
+        <v>6939</v>
+      </c>
+      <c r="D65" t="s">
+        <v>251</v>
+      </c>
+      <c r="E65" t="s">
+        <v>252</v>
+      </c>
+      <c r="F65" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>254</v>
+      </c>
+      <c r="B66" t="n">
+        <v>142</v>
+      </c>
+      <c r="C66" t="n">
+        <v>2364</v>
+      </c>
+      <c r="D66" t="s">
+        <v>255</v>
+      </c>
+      <c r="E66" t="s">
+        <v>256</v>
+      </c>
+      <c r="F66" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>258</v>
+      </c>
+      <c r="B67" t="n">
+        <v>217</v>
+      </c>
+      <c r="C67" t="n">
+        <v>3092</v>
+      </c>
+      <c r="D67" t="s">
+        <v>259</v>
+      </c>
+      <c r="E67" t="s">
+        <v>260</v>
+      </c>
+      <c r="F67" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>262</v>
+      </c>
+      <c r="B68" t="n">
+        <v>326</v>
+      </c>
+      <c r="C68" t="n">
+        <v>6080</v>
+      </c>
+      <c r="D68" t="s">
+        <v>263</v>
+      </c>
+      <c r="E68" t="s">
+        <v>264</v>
+      </c>
+      <c r="F68" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>266</v>
+      </c>
+      <c r="B69" t="n">
+        <v>103</v>
+      </c>
+      <c r="C69" t="n">
+        <v>809</v>
+      </c>
+      <c r="D69" t="s">
+        <v>267</v>
+      </c>
+      <c r="E69" t="s">
+        <v>268</v>
+      </c>
+      <c r="F69" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>270</v>
+      </c>
+      <c r="B70" t="n">
+        <v>101</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3617</v>
+      </c>
+      <c r="D70" t="s">
+        <v>271</v>
+      </c>
+      <c r="E70" t="s">
+        <v>272</v>
+      </c>
+      <c r="F70" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>274</v>
+      </c>
+      <c r="B71" t="n">
+        <v>244</v>
+      </c>
+      <c r="C71" t="n">
+        <v>6736</v>
+      </c>
+      <c r="D71" t="s">
+        <v>275</v>
+      </c>
+      <c r="E71" t="s">
+        <v>276</v>
+      </c>
+      <c r="F71" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>278</v>
+      </c>
+      <c r="B72" t="n">
+        <v>147</v>
+      </c>
+      <c r="C72" t="n">
+        <v>2858</v>
+      </c>
+      <c r="D72" t="s">
+        <v>279</v>
+      </c>
+      <c r="E72" t="s">
+        <v>280</v>
+      </c>
+      <c r="F72" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>282</v>
+      </c>
+      <c r="B73" t="n">
+        <v>102</v>
+      </c>
+      <c r="C73" t="n">
+        <v>2450</v>
+      </c>
+      <c r="D73" t="s">
+        <v>283</v>
+      </c>
+      <c r="E73" t="s">
+        <v>284</v>
+      </c>
+      <c r="F73" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>286</v>
+      </c>
+      <c r="B74" t="n">
+        <v>138</v>
+      </c>
+      <c r="C74" t="n">
+        <v>2990</v>
+      </c>
+      <c r="D74" t="s">
+        <v>287</v>
+      </c>
+      <c r="E74" t="s">
+        <v>288</v>
+      </c>
+      <c r="F74" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>290</v>
+      </c>
+      <c r="B75" t="n">
+        <v>400</v>
+      </c>
+      <c r="C75" t="n">
+        <v>5815</v>
+      </c>
+      <c r="D75" t="s">
+        <v>291</v>
+      </c>
+      <c r="E75" t="s">
+        <v>292</v>
+      </c>
+      <c r="F75" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>294</v>
+      </c>
+      <c r="B76" t="n">
+        <v>236</v>
+      </c>
+      <c r="C76" t="n">
+        <v>3011</v>
+      </c>
+      <c r="D76" t="s">
+        <v>295</v>
+      </c>
+      <c r="E76" t="s">
+        <v>296</v>
+      </c>
+      <c r="F76" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>298</v>
+      </c>
+      <c r="B77" t="n">
+        <v>220</v>
+      </c>
+      <c r="C77" t="n">
+        <v>5365</v>
+      </c>
+      <c r="D77" t="s">
+        <v>299</v>
+      </c>
+      <c r="E77" t="s">
+        <v>300</v>
+      </c>
+      <c r="F77" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>302</v>
+      </c>
+      <c r="B78" t="n">
+        <v>68</v>
+      </c>
+      <c r="C78" t="n">
+        <v>2968</v>
+      </c>
+      <c r="D78" t="s">
+        <v>303</v>
+      </c>
+      <c r="E78" t="s">
+        <v>304</v>
+      </c>
+      <c r="F78" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>306</v>
+      </c>
+      <c r="B79" t="n">
+        <v>380</v>
+      </c>
+      <c r="C79" t="n">
+        <v>5363</v>
+      </c>
+      <c r="D79" t="s">
+        <v>307</v>
+      </c>
+      <c r="E79" t="s">
+        <v>308</v>
+      </c>
+      <c r="F79" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>310</v>
+      </c>
+      <c r="B80" t="n">
+        <v>76</v>
+      </c>
+      <c r="C80" t="n">
+        <v>3453</v>
+      </c>
+      <c r="D80" t="s">
+        <v>311</v>
+      </c>
+      <c r="E80" t="s">
+        <v>312</v>
+      </c>
+      <c r="F80" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>314</v>
+      </c>
+      <c r="B81" t="n">
+        <v>4</v>
+      </c>
+      <c r="C81" t="n">
+        <v>51</v>
+      </c>
+      <c r="D81" t="s">
+        <v>205</v>
+      </c>
+      <c r="E81" t="s">
+        <v>205</v>
+      </c>
+      <c r="F81" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>316</v>
+      </c>
+      <c r="B82" t="n">
+        <v>166</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1633</v>
+      </c>
+      <c r="D82" t="s">
+        <v>317</v>
+      </c>
+      <c r="E82" t="s">
+        <v>303</v>
+      </c>
+      <c r="F82" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>319</v>
+      </c>
+      <c r="B83" t="n">
+        <v>223</v>
+      </c>
+      <c r="C83" t="n">
+        <v>4738</v>
+      </c>
+      <c r="D83" t="s">
+        <v>320</v>
+      </c>
+      <c r="E83" t="s">
+        <v>321</v>
+      </c>
+      <c r="F83" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>323</v>
+      </c>
+      <c r="B84" t="n">
+        <v>32</v>
+      </c>
+      <c r="C84" t="n">
+        <v>788</v>
+      </c>
+      <c r="D84" t="s">
+        <v>324</v>
+      </c>
+      <c r="E84" t="s">
+        <v>325</v>
+      </c>
+      <c r="F84" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>327</v>
+      </c>
+      <c r="B85" t="n">
+        <v>199</v>
+      </c>
+      <c r="C85" t="n">
+        <v>2594</v>
+      </c>
+      <c r="D85" t="s">
+        <v>328</v>
+      </c>
+      <c r="E85" t="s">
+        <v>329</v>
+      </c>
+      <c r="F85" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>331</v>
+      </c>
+      <c r="B86" t="n">
+        <v>66</v>
+      </c>
+      <c r="C86" t="n">
+        <v>2724</v>
+      </c>
+      <c r="D86" t="s">
+        <v>332</v>
+      </c>
+      <c r="E86" t="s">
+        <v>333</v>
+      </c>
+      <c r="F86" t="s">
+        <v>334</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
